--- a/assests/Day_2_Climate_Risk_Stress_Test_Model.xlsx
+++ b/assests/Day_2_Climate_Risk_Stress_Test_Model.xlsx
@@ -5,19 +5,21 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sanaq\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Training programs\environment\climate scenario\case studies\case study day 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D4C735-4102-44A3-9204-2A428D7D35AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{899B034B-803E-4826-AFDB-0D51D00F4029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Portfolio Setup" sheetId="2" r:id="rId2"/>
-    <sheet name="Transition Risk Quantification" sheetId="3" r:id="rId3"/>
-    <sheet name="Physical Risk Quantification" sheetId="4" r:id="rId4"/>
-    <sheet name="Strategic Response &amp; Mitigation" sheetId="5" r:id="rId5"/>
+    <sheet name="reference" sheetId="6" r:id="rId3"/>
+    <sheet name="Grid" sheetId="7" r:id="rId4"/>
+    <sheet name="Transition Risk Quantification" sheetId="3" r:id="rId5"/>
+    <sheet name="Physical Risk Quantification" sheetId="4" r:id="rId6"/>
+    <sheet name="Strategic Response &amp; Mitigation" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="134">
   <si>
     <t>Climate Stress Test Model - Executive Dashboard</t>
   </si>
@@ -265,17 +267,445 @@
   </si>
   <si>
     <t>Operational Shielding: Heat-resistant composite infrastructure cooling</t>
+  </si>
+  <si>
+    <t>Absolute Physical Emissions</t>
+  </si>
+  <si>
+    <t>Metric tons</t>
+  </si>
+  <si>
+    <t>NGFS Carbon price</t>
+  </si>
+  <si>
+    <t>Financial scale</t>
+  </si>
+  <si>
+    <t>Scenario / Pathway</t>
+  </si>
+  <si>
+    <t>Core Source</t>
+  </si>
+  <si>
+    <t>Transition Variable: Carbon Price ($/tCO₂e)</t>
+  </si>
+  <si>
+    <t>Transition Variable: Sector Market Drop (%)</t>
+  </si>
+  <si>
+    <t>Physical Variable: Extreme Shock Weight (Δ)</t>
+  </si>
+  <si>
+    <t>Physical Variable: Chronic Output Degradation (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NGFS / IEA </t>
+  </si>
+  <si>
+    <t>1.0x</t>
+  </si>
+  <si>
+    <t>Disorderly (Delayed)</t>
+  </si>
+  <si>
+    <t>Hot House World</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NGFS / IPCC </t>
+  </si>
+  <si>
+    <t>3.5x</t>
+  </si>
+  <si>
+    <t>Step 1: Establish the Centralized "Scenario Parameters" Input Grid</t>
+  </si>
+  <si>
+    <t>Step 2: Extract and Input NGFS / IEA Transition Data</t>
+  </si>
+  <si>
+    <t>High macroeconomic spillovers via reduced labor capacity.</t>
+  </si>
+  <si>
+    <t>Extreme Temperature Shocks</t>
+  </si>
+  <si>
+    <t>Immediate credit rating downgrades for Agricultural &amp; Food sectors.</t>
+  </si>
+  <si>
+    <t>Crop Yield &amp; Drought Shocks</t>
+  </si>
+  <si>
+    <t>Long-term operational constraints; utility cost spikes.</t>
+  </si>
+  <si>
+    <t>Chronic Water Stress</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Severe supply chain and port blockages in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>DIRE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>DAPS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Coastal Flood / Cyclone Risk</t>
+  </si>
+  <si>
+    <t>High physical damage to infrastructure during DAPS "Wet" years.</t>
+  </si>
+  <si>
+    <t>Fluvial Flood Risk</t>
+  </si>
+  <si>
+    <t>Primary Scenario Impact</t>
+  </si>
+  <si>
+    <t>Time Horizon</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Hazard/ Physincal Risk</t>
+  </si>
+  <si>
+    <t>Risks related scenarios (Short Term) mapping with NGFS Short Term Scenarios</t>
+  </si>
+  <si>
+    <t>2030-2050</t>
+  </si>
+  <si>
+    <t>Target Column in Your Excel Template</t>
+  </si>
+  <si>
+    <t>NGFS Source File</t>
+  </si>
+  <si>
+    <t>NGFS Row Variable Filter (Variable Column)</t>
+  </si>
+  <si>
+    <t>How to Calculate &amp; Input the Number</t>
+  </si>
+  <si>
+    <r>
+      <t>Transition Risk:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Carbon Tax Liability</t>
+    </r>
+  </si>
+  <si>
+    <t>GEME3_IIASA</t>
+  </si>
+  <si>
+    <r>
+      <t>Transition Risk:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Sector Market Drop (%)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[Your Target Sector]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>(e.g.,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Production</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Physical Risk:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Acute Asset Destruction</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>direct_impacts_daps</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>direct_impacts_dire</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>capital_destruction|coastal_flood|[Sector]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (or </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>riverine_flood</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Copy the raw percentage value listed in the target year column (e.g., 2030 or 2050) under the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>HWTP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>DAPS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> scenario. Multiply this directly against your asset's Net Book Value.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Physical Risk:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Chronic Productivity Loss</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Production|Agriculture</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (or relevant manufacturing indices)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Extract the multi-decade output drop from the updated </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>NGFS Phase V damage functions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. Input the delta (e.g., </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>24.0%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> for extreme Hot House stress) into your chronic operational calculators.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Risk Management:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Central ERM Integration</t>
+    </r>
+  </si>
+  <si>
+    <t>CLIMACRED_IIASA</t>
+  </si>
+  <si>
+    <t>baseline_pd|[Your Asset Sector]</t>
+  </si>
+  <si>
+    <t>Track the delta between the baseline Probability of Default (PD) and the scenario-stressed PD to calibrate your corporate risk severity score.</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Production</t>
+  </si>
+  <si>
+    <t>Carbon (or Sector energy cost proxies)</t>
+  </si>
+  <si>
+    <t>Step 1: Establish the Centralized "Scenario Parameters" Input Grid - Short Term</t>
+  </si>
+  <si>
+    <t>4x</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="5">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="\$#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -288,27 +718,80 @@
       <sz val="16"/>
       <color rgb="FF1E3F20"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF555555"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Google Sans Text"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -349,7 +832,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -383,11 +866,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -483,9 +982,49 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1198,23 +1737,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="78" customWidth="1"/>
     <col min="2" max="4" width="41" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1228,7 +1767,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
@@ -1245,7 +1784,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
         <v>7</v>
       </c>
@@ -1262,7 +1801,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4">
       <c r="A7" s="7" t="s">
         <v>8</v>
       </c>
@@ -1279,7 +1818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8" s="7" t="s">
         <v>9</v>
       </c>
@@ -1296,7 +1835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" s="7" t="s">
         <v>10</v>
       </c>
@@ -1313,7 +1852,7 @@
         <v>356.5</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" s="7" t="s">
         <v>11</v>
       </c>
@@ -1330,7 +1869,7 @@
         <v>160.1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11" s="7" t="s">
         <v>12</v>
       </c>
@@ -1347,7 +1886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4">
       <c r="A12" s="8" t="s">
         <v>13</v>
       </c>
@@ -1364,7 +1903,7 @@
         <v>516.6</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
         <v>14</v>
       </c>
@@ -1381,7 +1920,7 @@
         <v>0.30210526315789477</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4">
       <c r="A14" s="7" t="s">
         <v>15</v>
       </c>
@@ -1406,8 +1945,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="74" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -1416,19 +1955,27 @@
     <col min="6" max="6" width="32" customWidth="1"/>
     <col min="7" max="7" width="23" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="10" max="10" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" ht="21">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13">
+      <c r="J3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="4" t="s">
         <v>18</v>
       </c>
@@ -1453,8 +2000,17 @@
       <c r="H4" s="4" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J4" s="35" t="s">
+        <v>76</v>
+      </c>
+      <c r="K4" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="L4" s="35" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="13" t="s">
         <v>26</v>
       </c>
@@ -1479,8 +2035,20 @@
       <c r="H5" s="14">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J5" s="36">
+        <f>D5*F5</f>
+        <v>81600</v>
+      </c>
+      <c r="K5">
+        <v>139</v>
+      </c>
+      <c r="L5" s="37">
+        <f>J5*K5</f>
+        <v>11342400</v>
+      </c>
+      <c r="M5" s="39"/>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="16" t="s">
         <v>29</v>
       </c>
@@ -1505,8 +2073,19 @@
       <c r="H6" s="18">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J6" s="36">
+        <f t="shared" ref="J6:J9" si="0">D6*F6</f>
+        <v>10200</v>
+      </c>
+      <c r="K6">
+        <v>139</v>
+      </c>
+      <c r="L6" s="37">
+        <f t="shared" ref="L6:L9" si="1">J6*K6</f>
+        <v>1417800</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="13" t="s">
         <v>32</v>
       </c>
@@ -1531,8 +2110,19 @@
       <c r="H7" s="14">
         <v>3.8</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J7" s="36">
+        <f t="shared" si="0"/>
+        <v>178500</v>
+      </c>
+      <c r="K7">
+        <v>139</v>
+      </c>
+      <c r="L7" s="37">
+        <f t="shared" si="1"/>
+        <v>24811500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="16" t="s">
         <v>35</v>
       </c>
@@ -1557,8 +2147,19 @@
       <c r="H8" s="18">
         <v>1.9</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J8" s="36">
+        <f t="shared" si="0"/>
+        <v>2925</v>
+      </c>
+      <c r="K8">
+        <v>139</v>
+      </c>
+      <c r="L8" s="37">
+        <f t="shared" si="1"/>
+        <v>406575</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="13" t="s">
         <v>38</v>
       </c>
@@ -1583,34 +2184,45 @@
       <c r="H9" s="14">
         <v>2.8</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J9" s="36">
+        <f t="shared" si="0"/>
+        <v>29400</v>
+      </c>
+      <c r="K9">
+        <v>139</v>
+      </c>
+      <c r="L9" s="37">
+        <f t="shared" si="1"/>
+        <v>4086600</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="20" t="s">
         <v>41</v>
       </c>
       <c r="B11" s="21"/>
       <c r="C11" s="22">
-        <f t="shared" ref="C11:H11" si="0">SUM(C5:C10)</f>
+        <f t="shared" ref="C11:H11" si="2">SUM(C5:C10)</f>
         <v>1710</v>
       </c>
       <c r="D11" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>620</v>
       </c>
       <c r="E11" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F11" s="23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1905</v>
       </c>
       <c r="G11" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1540</v>
       </c>
       <c r="H11" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>18.2</v>
       </c>
     </row>
@@ -1620,9 +2232,362 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6771F6BF-D0B2-41DE-A6BD-7CD908E4B332}">
+  <dimension ref="B3:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="28.5703125" customWidth="1"/>
+    <col min="3" max="3" width="31.5703125" customWidth="1"/>
+    <col min="4" max="4" width="36.28515625" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="14" width="44.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:4">
+      <c r="B3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" ht="15.75" thickBot="1"/>
+    <row r="5" spans="2:4" ht="15.75" thickBot="1">
+      <c r="B5" s="40" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" s="40" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="43.5" thickBot="1">
+      <c r="B6" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="29.25" thickBot="1">
+      <c r="B7" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="29.25" thickBot="1">
+      <c r="B8" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="29.25" thickBot="1">
+      <c r="B9" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" ht="29.25" thickBot="1">
+      <c r="B10" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" s="41" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DE5A4B3-D977-41BF-84E7-BE88B2F5E8C5}">
+  <dimension ref="B2:N14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="23.5703125" customWidth="1"/>
+    <col min="3" max="4" width="17" customWidth="1"/>
+    <col min="5" max="8" width="23.7109375" customWidth="1"/>
+    <col min="11" max="13" width="26" customWidth="1"/>
+    <col min="14" max="14" width="51.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14">
+      <c r="B2" s="48" t="s">
+        <v>92</v>
+      </c>
+      <c r="K2" s="48" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" ht="15.75" thickBot="1">
+      <c r="B3" s="38"/>
+    </row>
+    <row r="4" spans="2:14" ht="45.75" thickBot="1">
+      <c r="B4" s="40" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="40" t="s">
+        <v>105</v>
+      </c>
+      <c r="E4" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="H4" s="40" t="s">
+        <v>85</v>
+      </c>
+      <c r="K4" s="40" t="s">
+        <v>110</v>
+      </c>
+      <c r="L4" s="40" t="s">
+        <v>111</v>
+      </c>
+      <c r="M4" s="40" t="s">
+        <v>112</v>
+      </c>
+      <c r="N4" s="40" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" ht="30.75" thickBot="1">
+      <c r="B5" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="E5" s="42">
+        <v>150</v>
+      </c>
+      <c r="F5" s="50">
+        <v>0.12</v>
+      </c>
+      <c r="G5" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="H5" s="45">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="K5" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="L5" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="M5" s="41" t="s">
+        <v>129</v>
+      </c>
+      <c r="N5" s="41" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" ht="30" thickBot="1">
+      <c r="B6" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="E6" s="42">
+        <v>250</v>
+      </c>
+      <c r="F6" s="50">
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="44" t="s">
+        <v>133</v>
+      </c>
+      <c r="H6" s="45">
+        <v>5.5E-2</v>
+      </c>
+      <c r="K6" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="L6" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="M6" s="52" t="s">
+        <v>130</v>
+      </c>
+      <c r="N6" s="52" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" ht="57.75" thickBot="1">
+      <c r="B7" s="40" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="E7" s="42">
+        <v>0</v>
+      </c>
+      <c r="F7" s="50">
+        <v>0</v>
+      </c>
+      <c r="G7" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="H7" s="45">
+        <v>0.24</v>
+      </c>
+      <c r="K7" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="L7" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="M7" s="44" t="s">
+        <v>120</v>
+      </c>
+      <c r="N7" s="41" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" ht="59.25" thickBot="1">
+      <c r="K8" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="L8" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="M8" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="N8" s="41" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" ht="43.5" thickBot="1">
+      <c r="B9" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="K9" s="40" t="s">
+        <v>125</v>
+      </c>
+      <c r="L9" s="44" t="s">
+        <v>126</v>
+      </c>
+      <c r="M9" s="44" t="s">
+        <v>127</v>
+      </c>
+      <c r="N9" s="41" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" ht="15.75" thickBot="1">
+      <c r="B10" s="38"/>
+    </row>
+    <row r="11" spans="2:14" ht="45.75" thickBot="1">
+      <c r="B11" s="40" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="40" t="s">
+        <v>105</v>
+      </c>
+      <c r="E11" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="F11" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="H11" s="40" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" ht="30.75" thickBot="1">
+      <c r="B12" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" s="41"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="45"/>
+    </row>
+    <row r="13" spans="2:14" ht="15.75" thickBot="1">
+      <c r="B13" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" s="41" t="s">
+        <v>86</v>
+      </c>
+      <c r="D13" s="41"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="45"/>
+    </row>
+    <row r="14" spans="2:14" ht="15.75" thickBot="1">
+      <c r="B14" s="40" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" s="41" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="41"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="45"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:N11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="43" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -1638,40 +2603,40 @@
     <col min="14" max="14" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="21">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="35" t="s">
+    <row r="4" spans="1:14">
+      <c r="A4" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35" t="s">
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35" t="s">
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="L4" s="35"/>
-      <c r="M4" s="35"/>
-      <c r="N4" s="35"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="35"/>
-      <c r="B5" s="35"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="46"/>
+      <c r="N4" s="46"/>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="46"/>
+      <c r="B5" s="46"/>
       <c r="C5" s="24" t="s">
         <v>47</v>
       </c>
@@ -1709,7 +2674,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14">
       <c r="A6" s="25" t="s">
         <v>26</v>
       </c>
@@ -1763,7 +2728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14">
       <c r="A7" s="29" t="s">
         <v>29</v>
       </c>
@@ -1817,7 +2782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14">
       <c r="A8" s="25" t="s">
         <v>32</v>
       </c>
@@ -1871,7 +2836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14">
       <c r="A9" s="29" t="s">
         <v>35</v>
       </c>
@@ -1925,7 +2890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14">
       <c r="A10" s="25" t="s">
         <v>38</v>
       </c>
@@ -1979,7 +2944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14">
       <c r="A11" s="20" t="s">
         <v>52</v>
       </c>
@@ -2032,6 +2997,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="C13" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2045,10 +3013,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -2065,40 +3033,40 @@
     <col min="14" max="14" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="21">
       <c r="A1" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="35" t="s">
+    <row r="4" spans="1:14">
+      <c r="A4" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35" t="s">
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35" t="s">
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="L4" s="35"/>
-      <c r="M4" s="35"/>
-      <c r="N4" s="35"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="35"/>
-      <c r="B5" s="35"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="46"/>
+      <c r="N4" s="46"/>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="46"/>
+      <c r="B5" s="46"/>
       <c r="C5" s="24" t="s">
         <v>57</v>
       </c>
@@ -2136,7 +3104,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14">
       <c r="A6" s="25" t="s">
         <v>26</v>
       </c>
@@ -2193,7 +3161,7 @@
         <v>109.8</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14">
       <c r="A7" s="29" t="s">
         <v>29</v>
       </c>
@@ -2250,7 +3218,7 @@
         <v>113.3</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14">
       <c r="A8" s="25" t="s">
         <v>32</v>
       </c>
@@ -2307,7 +3275,7 @@
         <v>136.80000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14">
       <c r="A9" s="29" t="s">
         <v>35</v>
       </c>
@@ -2364,7 +3332,7 @@
         <v>58.3</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14">
       <c r="A10" s="25" t="s">
         <v>38</v>
       </c>
@@ -2421,7 +3389,7 @@
         <v>98.4</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14">
       <c r="A11" s="20" t="s">
         <v>52</v>
       </c>
@@ -2487,10 +3455,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:O11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
     <col min="2" max="2" width="81" customWidth="1"/>
@@ -2509,44 +3477,44 @@
     <col min="15" max="15" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="21">
       <c r="A1" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="35" t="s">
+    <row r="4" spans="1:15">
+      <c r="A4" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="46" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="D4" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35" t="s">
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="35" t="s">
+      <c r="I4" s="46"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="M4" s="35"/>
-      <c r="N4" s="35"/>
-      <c r="O4" s="35"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="35"/>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
+      <c r="M4" s="46"/>
+      <c r="N4" s="46"/>
+      <c r="O4" s="46"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="46"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
       <c r="D5" s="24" t="s">
         <v>67</v>
       </c>
@@ -2584,7 +3552,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15">
       <c r="A6" s="25" t="s">
         <v>26</v>
       </c>
@@ -2640,7 +3608,7 @@
         <v>-23.040000000000006</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15">
       <c r="A7" s="29" t="s">
         <v>29</v>
       </c>
@@ -2696,7 +3664,7 @@
         <v>26.65</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15">
       <c r="A8" s="25" t="s">
         <v>32</v>
       </c>
@@ -2752,7 +3720,7 @@
         <v>22.879999999999995</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15">
       <c r="A9" s="29" t="s">
         <v>35</v>
       </c>
@@ -2808,7 +3776,7 @@
         <v>2.490000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15">
       <c r="A10" s="25" t="s">
         <v>38</v>
       </c>
@@ -2864,7 +3832,7 @@
         <v>24.28</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15">
       <c r="A11" s="20" t="s">
         <v>52</v>
       </c>
